--- a/outputs/cluster_assignments_expert_seeded_all_strategies.xlsx
+++ b/outputs/cluster_assignments_expert_seeded_all_strategies.xlsx
@@ -16,10 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S6_contrast" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M1_label_prop" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M2_rule_based" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M3_consensus" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement_Strategies" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement_byAlgo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verkostung_Compare" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M1_kw" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M2_kw" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M3_consensus" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement_Strategies" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement_byAlgo" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verkostung_Compare" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:N131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +500,16 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>M1_kw</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>M3_consensus</t>
         </is>
       </c>
@@ -550,6 +562,16 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>dairy</t>
         </is>
       </c>
@@ -602,6 +624,16 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>floral</t>
         </is>
       </c>
@@ -654,6 +686,16 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -706,6 +748,16 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -758,6 +810,16 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>warm</t>
         </is>
       </c>
@@ -820,6 +882,16 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>floral</t>
         </is>
       </c>
@@ -872,6 +944,16 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -924,6 +1006,16 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -976,6 +1068,16 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -1028,6 +1130,16 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -1080,6 +1192,16 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -1132,6 +1254,16 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -1184,6 +1316,16 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -1236,6 +1378,16 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -1288,6 +1440,16 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -1340,6 +1502,16 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -1392,6 +1564,16 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -1447,6 +1629,16 @@
           <t>fruity</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1496,6 +1688,16 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>warm</t>
         </is>
       </c>
@@ -1548,6 +1750,16 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -1603,6 +1815,16 @@
           <t>fruity</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1652,6 +1874,16 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -1704,6 +1936,16 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -1766,6 +2008,16 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -1818,6 +2070,16 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -1870,6 +2132,16 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -1922,6 +2194,16 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>floral</t>
         </is>
       </c>
@@ -1974,6 +2256,16 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -2026,6 +2318,16 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>warm</t>
         </is>
       </c>
@@ -2078,6 +2380,16 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>warm</t>
         </is>
       </c>
@@ -2130,6 +2442,16 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -2182,6 +2504,16 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>dairy</t>
         </is>
       </c>
@@ -2234,6 +2566,16 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -2296,6 +2638,16 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -2351,6 +2703,16 @@
           <t>dairy</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2403,6 +2765,16 @@
           <t>green</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2452,6 +2824,16 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -2504,6 +2886,16 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -2556,6 +2948,16 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -2608,6 +3010,16 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -2660,6 +3072,16 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -2712,6 +3134,16 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -2767,6 +3199,16 @@
           <t>unpleasant</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2816,6 +3258,16 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t>warm</t>
         </is>
       </c>
@@ -2868,6 +3320,16 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -2920,6 +3382,16 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -2975,6 +3447,16 @@
           <t>fruity</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3024,6 +3506,16 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -3076,6 +3568,16 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -3128,6 +3630,16 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>floral</t>
         </is>
       </c>
@@ -3180,6 +3692,16 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
           <t>dairy</t>
         </is>
       </c>
@@ -3232,6 +3754,16 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -3284,6 +3816,16 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -3339,6 +3881,16 @@
           <t>green</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3388,6 +3940,16 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -3443,6 +4005,16 @@
           <t>Walderdbeere</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3492,6 +4064,16 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -3544,6 +4126,16 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -3609,6 +4201,16 @@
           <t>dairy</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3658,6 +4260,16 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -3710,6 +4322,16 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
           <t>warm</t>
         </is>
       </c>
@@ -3762,6 +4384,16 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -3814,6 +4446,16 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -3869,6 +4511,16 @@
           <t>green</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3931,6 +4583,16 @@
           <t>unpleasant</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3983,6 +4645,16 @@
           <t>dairy</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4035,6 +4707,16 @@
           <t>dairy</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4084,6 +4766,16 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
           <t>dairy</t>
         </is>
       </c>
@@ -4136,6 +4828,16 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -4188,6 +4890,16 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
           <t>dairy</t>
         </is>
       </c>
@@ -4240,6 +4952,16 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
           <t>dairy</t>
         </is>
       </c>
@@ -4292,6 +5014,16 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -4344,6 +5076,16 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -4396,6 +5138,16 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
           <t>dairy</t>
         </is>
       </c>
@@ -4448,6 +5200,16 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
           <t>warm</t>
         </is>
       </c>
@@ -4503,6 +5265,16 @@
           <t>dairy</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4552,6 +5324,16 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -4604,6 +5386,16 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -4656,6 +5448,16 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
           <t>warm</t>
         </is>
       </c>
@@ -4708,6 +5510,16 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
           <t>dairy</t>
         </is>
       </c>
@@ -4760,6 +5572,16 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -4812,6 +5634,16 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -4877,6 +5709,16 @@
           <t>green</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4926,6 +5768,16 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -4978,6 +5830,16 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -5030,6 +5892,16 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
           <t>dairy</t>
         </is>
       </c>
@@ -5082,6 +5954,16 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -5144,6 +6026,16 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -5199,6 +6091,16 @@
           <t>dairy</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5251,6 +6153,16 @@
           <t>unpleasant</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5300,6 +6212,16 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
           <t>warm</t>
         </is>
       </c>
@@ -5352,6 +6274,16 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -5417,6 +6349,16 @@
           <t>Walderdbeere</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5466,6 +6408,16 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -5521,6 +6473,16 @@
           <t>dairy</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5570,6 +6532,16 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
           <t>warm</t>
         </is>
       </c>
@@ -5622,6 +6594,16 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -5677,6 +6659,16 @@
           <t>dairy</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5726,6 +6718,16 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -5781,6 +6783,16 @@
           <t>dairy</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5843,6 +6855,16 @@
           <t>green</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5892,6 +6914,16 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -5944,6 +6976,16 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -5999,6 +7041,16 @@
           <t>dairy</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6048,6 +7100,16 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -6100,6 +7162,16 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -6152,6 +7224,16 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -6204,6 +7286,16 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
@@ -6259,6 +7351,16 @@
           <t>green</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6311,6 +7413,16 @@
           <t>green</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6360,6 +7472,16 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
           <t>floral</t>
         </is>
       </c>
@@ -6412,6 +7534,16 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -6467,6 +7599,16 @@
           <t>dairy</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6519,6 +7661,16 @@
           <t>unpleasant</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6571,6 +7723,16 @@
           <t>unpleasant</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6620,6 +7782,16 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -6672,6 +7844,16 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -6727,6 +7909,16 @@
           <t>unpleasant</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6776,6 +7968,16 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
           <t>dairy</t>
         </is>
       </c>
@@ -6841,6 +8043,16 @@
           <t>fruity</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6890,6 +8102,16 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
           <t>warm</t>
         </is>
       </c>
@@ -6942,6 +8164,16 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -6994,6 +8226,16 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -7046,6 +8288,16 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
           <t>floral</t>
         </is>
       </c>
@@ -7098,6 +8350,16 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -7150,6 +8412,16 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -7202,6 +8474,16 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -7264,6 +8546,16 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
           <t>floral</t>
         </is>
       </c>
@@ -7319,6 +8611,16 @@
           <t>dairy</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7367,6 +8669,16 @@
         </is>
       </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -7378,6 +8690,448 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_Walderdbeere</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_dairy</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_floral</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_fruity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_green</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_unpleasant</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>M1_kw</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>185.621P
+187.894P
+188.976</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>185.291
+185.294
+185.471
+186.985P
+187.167P
+187.826P
+187.886P
+187.907
+187.921P
+187.923P
+188.402P
+188.656P</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>185.046
+185.321
+185.644P
+185.675P
+186.190P
+186.192
+186.981P
+187.015P
+187.776
+187.786P
+187.796P
+187.885P
+187.914P
+189.014</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>185.028
+185.513P
+185.727P
+187.004P
+187.695P
+187.772
+187.893P
+188.481KHP
+188.639P</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>185.086
+185.178HP
+185.382P
+185.507P
+186.569P
+187.246P
+187.482P
+187.483P
+187.519P
+187.657P
+187.746P
+187.787P
+187.834P
+187.920P
+188.375P
+188.412P
+188.560P
+188.820
+188.894</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>185.133
+185.267
+186.821
+187.414P
+187.773P
+187.829P</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>185.043P
+185.044
+185.090P
+185.091
+185.237H
+185.239
+185.309P
+185.314
+185.339P
+185.514
+185.578P
+185.615
+185.664
+185.741P
+185.748P
+185.796P
+185.902P
+185.922P
+185.984P
+186.179P
+186.277P
+186.293P
+186.395P
+186.396P
+186.490P
+186.950P
+187.061P
+187.064P
+187.119P
+187.365
+187.507P
+187.521P
+187.522P
+187.567P
+187.571P
+187.608P
+187.662P
+187.694P
+187.752P
+187.753P
+187.783P
+187.791P
+187.799P
+187.800P
+187.843P
+187.870P
+187.871P
+187.892P
+187.895P
+187.896P
+187.897P
+187.916P
+188.118P
+188.462KHP
+188.491P
+188.628P
+188.668P
+188.740P
+188.819
+188.822
+188.866
+188.977
+188.992
+189.012
+189.051
+189.068
+189.075</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_Walderdbeere</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_dairy</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_floral</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_fruity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_green</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_unpleasant</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster_warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>186.985P
+187.892P
+187.894P
+187.897P
+188.976
+189.012
+189.051</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>185.291
+185.294
+185.471
+185.578P
+185.748P
+187.167P
+187.483P
+187.662P
+187.746P
+187.791P
+187.826P
+187.886P
+187.896P
+187.907
+187.921P
+188.118P
+188.402P
+188.656P
+188.668P</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>185.046
+185.902P
+185.922P
+185.984P
+187.064P
+187.365
+187.414P
+187.776
+187.783P
+187.786P
+187.796P
+187.834P
+189.014
+189.075</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>185.028
+185.239
+185.513P
+185.727P
+186.190P
+186.192
+187.061P
+187.752P
+187.753P
+187.871P
+188.822</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>185.178HP
+186.569P
+187.246P
+187.519P
+187.521P
+188.412P
+188.560P</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>185.043P
+185.044
+185.086
+185.090P
+185.091
+185.133
+185.514
+185.615
+185.741P
+186.293P
+186.821
+187.657P
+187.773P
+187.787P
+187.799P
+187.829P
+187.843P
+187.885P
+187.895P
+188.375P
+188.639P
+188.819
+188.866
+189.068</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>185.237H
+185.267
+185.309P
+185.314
+185.321
+185.339P
+185.382P
+185.507P
+185.621P
+185.644P
+185.664
+185.675P
+185.796P
+186.179P
+186.277P
+186.395P
+186.396P
+186.490P
+186.950P
+186.981P
+187.004P
+187.015P
+187.119P
+187.482P
+187.507P
+187.522P
+187.567P
+187.571P
+187.608P
+187.694P
+187.695P
+187.772
+187.800P
+187.870P
+187.893P
+187.914P
+187.916P
+187.920P
+187.923P
+188.462KHP
+188.481KHP
+188.491P
+188.628P
+188.740P
+188.820
+188.894
+188.977
+188.992</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7598,13 +9352,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7763,50 +9517,50 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M3_consensus</t>
+          <t>M1_kw</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.647</v>
+        <v>0.149</v>
       </c>
       <c r="D9" t="n">
-        <v>0.712</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S2_ingredients</t>
+          <t>S1_target_recipes</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S3_hybrid</t>
+          <t>M2_kw</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.508</v>
+        <v>0.22</v>
       </c>
       <c r="D10" t="n">
-        <v>0.54</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S2_ingredients</t>
+          <t>S1_target_recipes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S4_target_recipes_median</t>
+          <t>M3_consensus</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.533</v>
+        <v>0.647</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="12">
@@ -7817,14 +9571,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S5_ingredients_median</t>
+          <t>S3_hybrid</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.57</v>
+        <v>0.508</v>
       </c>
       <c r="D12" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="13">
@@ -7835,14 +9589,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S6_contrast</t>
+          <t>S4_target_recipes_median</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.408</v>
+        <v>0.533</v>
       </c>
       <c r="D13" t="n">
-        <v>0.53</v>
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -7853,14 +9607,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M1_label_prop</t>
+          <t>S5_ingredients_median</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.194</v>
+        <v>0.57</v>
       </c>
       <c r="D14" t="n">
-        <v>0.39</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="15">
@@ -7871,14 +9625,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M2_rule_based</t>
+          <t>S6_contrast</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.194</v>
+        <v>0.408</v>
       </c>
       <c r="D15" t="n">
-        <v>0.324</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="16">
@@ -7889,86 +9643,86 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M3_consensus</t>
+          <t>M1_label_prop</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.501</v>
+        <v>0.194</v>
       </c>
       <c r="D16" t="n">
-        <v>0.616</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S3_hybrid</t>
+          <t>S2_ingredients</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S4_target_recipes_median</t>
+          <t>M2_rule_based</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.922</v>
+        <v>0.194</v>
       </c>
       <c r="D17" t="n">
-        <v>0.905</v>
+        <v>0.324</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S3_hybrid</t>
+          <t>S2_ingredients</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S5_ingredients_median</t>
+          <t>M1_kw</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.487</v>
+        <v>0.106</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.287</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S3_hybrid</t>
+          <t>S2_ingredients</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S6_contrast</t>
+          <t>M2_kw</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.593</v>
+        <v>0.183</v>
       </c>
       <c r="D19" t="n">
-        <v>0.702</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S3_hybrid</t>
+          <t>S2_ingredients</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M1_label_prop</t>
+          <t>M3_consensus</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.279</v>
+        <v>0.501</v>
       </c>
       <c r="D20" t="n">
-        <v>0.48</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="21">
@@ -7979,14 +9733,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M2_rule_based</t>
+          <t>S4_target_recipes_median</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.212</v>
+        <v>0.922</v>
       </c>
       <c r="D21" t="n">
-        <v>0.369</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="22">
@@ -7997,284 +9751,626 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M3_consensus</t>
+          <t>S5_ingredients_median</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.637</v>
+        <v>0.487</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S4_target_recipes_median</t>
+          <t>S3_hybrid</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S5_ingredients_median</t>
+          <t>S6_contrast</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.494</v>
+        <v>0.593</v>
       </c>
       <c r="D23" t="n">
-        <v>0.569</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S4_target_recipes_median</t>
+          <t>S3_hybrid</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S6_contrast</t>
+          <t>M1_label_prop</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.595</v>
+        <v>0.279</v>
       </c>
       <c r="D24" t="n">
-        <v>0.703</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S4_target_recipes_median</t>
+          <t>S3_hybrid</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M1_label_prop</t>
+          <t>M2_rule_based</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.292</v>
+        <v>0.212</v>
       </c>
       <c r="D25" t="n">
-        <v>0.511</v>
+        <v>0.369</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S4_target_recipes_median</t>
+          <t>S3_hybrid</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2_rule_based</t>
+          <t>M1_kw</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.223</v>
+        <v>0.118</v>
       </c>
       <c r="D26" t="n">
-        <v>0.401</v>
+        <v>0.356</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S4_target_recipes_median</t>
+          <t>S3_hybrid</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M3_consensus</t>
+          <t>M2_kw</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.624</v>
+        <v>0.201</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.354</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S5_ingredients_median</t>
+          <t>S3_hybrid</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S6_contrast</t>
+          <t>M3_consensus</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.334</v>
+        <v>0.637</v>
       </c>
       <c r="D28" t="n">
-        <v>0.504</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>S5_ingredients_median</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>M1_label_prop</t>
-        </is>
-      </c>
       <c r="C29" t="n">
-        <v>0.19</v>
+        <v>0.494</v>
       </c>
       <c r="D29" t="n">
-        <v>0.394</v>
+        <v>0.569</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S5_ingredients_median</t>
+          <t>S4_target_recipes_median</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M2_rule_based</t>
+          <t>S6_contrast</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.193</v>
+        <v>0.595</v>
       </c>
       <c r="D30" t="n">
-        <v>0.319</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S5_ingredients_median</t>
+          <t>S4_target_recipes_median</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M3_consensus</t>
+          <t>M1_label_prop</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.442</v>
+        <v>0.292</v>
       </c>
       <c r="D31" t="n">
-        <v>0.587</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S6_contrast</t>
+          <t>S4_target_recipes_median</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>M1_label_prop</t>
+          <t>M2_rule_based</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.235</v>
+        <v>0.223</v>
       </c>
       <c r="D32" t="n">
-        <v>0.428</v>
+        <v>0.401</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S6_contrast</t>
+          <t>S4_target_recipes_median</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M2_rule_based</t>
+          <t>M1_kw</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.202</v>
+        <v>0.137</v>
       </c>
       <c r="D33" t="n">
-        <v>0.354</v>
+        <v>0.379</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S6_contrast</t>
+          <t>S4_target_recipes_median</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>M3_consensus</t>
+          <t>M2_kw</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.669</v>
+        <v>0.211</v>
       </c>
       <c r="D34" t="n">
-        <v>0.702</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>M1_label_prop</t>
+          <t>S4_target_recipes_median</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>M2_rule_based</t>
+          <t>M3_consensus</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.103</v>
+        <v>0.624</v>
       </c>
       <c r="D35" t="n">
-        <v>0.281</v>
+        <v>0.6889999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>M1_label_prop</t>
+          <t>S5_ingredients_median</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>M3_consensus</t>
+          <t>S6_contrast</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.318</v>
+        <v>0.334</v>
       </c>
       <c r="D36" t="n">
-        <v>0.543</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.394</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>M2_rule_based</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C38" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.319</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M1_kw</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.332</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.302</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>M3_consensus</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C41" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.587</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.428</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>M1_kw</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.342</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.702</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.281</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>M1_kw</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.658</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.279</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>M1_kw</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.221</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
         <v>0.171</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D53" t="n">
         <v>0.323</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>M1_kw</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.237</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>M1_kw</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.367</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.303</v>
       </c>
     </row>
   </sheetData>
@@ -8282,7 +10378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9520,13 +11616,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9557,30 +11653,55 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>M1_kw</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>M1kw_vs_M1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>old_M2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>new_M2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>M2_change</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>M2kw_vs_M2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>kw_vote</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>panel_%</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Cluster_vorgegeben</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Jan_Free_Sorting</t>
         </is>
@@ -9613,21 +11734,34 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
         <v>100</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Karamell</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Karamell</t>
         </is>
@@ -9657,24 +11791,45 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>green</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
         <v>25</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>buttrig</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Heidelbeere/ Jasmin</t>
         </is>
@@ -9704,24 +11859,37 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
         <v>50</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>grün</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9747,24 +11915,45 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>green</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>75</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>grün - reif/ muffig</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9793,21 +11982,38 @@
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>100</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Walderdbeere</t>
         </is>
@@ -9840,21 +12046,34 @@
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
         <v>25</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>nicht verkostet</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>nicht verkostet</t>
         </is>
@@ -9889,19 +12108,40 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
         <v>50</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>blumig</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9932,19 +12172,36 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
         <v>25</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>blumig</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9973,21 +12230,38 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
         <v>50</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>grün</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Heidelbeere/ Jasmin</t>
         </is>
@@ -10020,21 +12294,34 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
         <v>75</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>nicht verkostet</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>nicht verkostet</t>
         </is>
@@ -10064,20 +12351,33 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="n">
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
         <v>50</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10106,21 +12406,34 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="n">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
         <v>50</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>buttrig - grün</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10149,21 +12462,34 @@
           <t>green</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="n">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
         <v>100</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>grün</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>grün</t>
         </is>
@@ -10193,20 +12519,37 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
         <v>25</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10232,24 +12575,45 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>floral</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
         <v>75</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>blumig</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10278,21 +12642,34 @@
           <t>green</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
         <v>50</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Karamell</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10321,21 +12698,38 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
         <v>75</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>buttrig</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>muffig/ buttrig</t>
         </is>
@@ -10370,19 +12764,40 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
         <v>50</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>nicht verkostet</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>nicht verkostet</t>
         </is>
@@ -10415,17 +12830,30 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="n">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
         <v>50</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10454,21 +12882,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="n">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
         <v>50</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>grün</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10497,25 +12938,42 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>RISK (panel liked old)</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
         <v>100</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>muffig</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Heidelbeere/ Jasmin</t>
         </is>
@@ -10545,24 +13003,49 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>green</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>floral</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>RISK (panel liked old)</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
         <v>75</v>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10591,21 +13074,34 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
         <v>75</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>reif/muffig</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10631,24 +13127,49 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>green</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
         <v>50</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>reif/muffig</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10677,21 +13198,38 @@
           <t>fruity</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="n">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
         <v>75</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>blumig</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Birne/ Marille (Outlayer)</t>
         </is>
@@ -10721,20 +13259,33 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="n">
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
         <v>100</v>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10763,21 +13314,34 @@
           <t>fruity</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
         <v>50</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>reif/ muffig</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10803,24 +13367,37 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="n">
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
         <v>25</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>reif/muffig</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/cluster_assignments_expert_seeded_all_strategies.xlsx
+++ b/outputs/cluster_assignments_expert_seeded_all_strategies.xlsx
@@ -16,12 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S6_contrast" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M1_label_prop" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M2_rule_based" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M1_kw" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M2_kw" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M3_consensus" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement_Strategies" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement_byAlgo" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verkostung_Compare" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M2_kw" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M3_consensus" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement_Strategies" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement_byAlgo" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verkostung_Compare" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N131"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,15 +499,10 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>M1_kw</t>
+          <t>M2_kw</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>M2_kw</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>M3_consensus</t>
         </is>
@@ -567,11 +561,6 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
           <t>dairy</t>
         </is>
       </c>
@@ -624,15 +613,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>fruity</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
@@ -686,15 +670,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -753,11 +732,6 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
           <t>green</t>
         </is>
       </c>
@@ -810,15 +784,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>floral</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
@@ -887,11 +856,6 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
           <t>floral</t>
         </is>
       </c>
@@ -944,15 +908,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -1011,11 +970,6 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -1068,15 +1022,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -1135,11 +1084,6 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -1197,11 +1141,6 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -1254,15 +1193,10 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
         <is>
           <t>Walderdbeere</t>
         </is>
@@ -1316,15 +1250,10 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -1378,15 +1307,10 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -1445,11 +1369,6 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -1507,11 +1426,6 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
           <t>green</t>
         </is>
       </c>
@@ -1569,11 +1483,6 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
           <t>green</t>
         </is>
       </c>
@@ -1626,15 +1535,10 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>fruity</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -1688,15 +1592,10 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>floral</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
@@ -1755,11 +1654,6 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -1812,15 +1706,10 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>fruity</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -1879,11 +1768,6 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -1936,15 +1820,10 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -2013,11 +1892,6 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -2075,11 +1949,6 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
           <t>green</t>
         </is>
       </c>
@@ -2132,15 +2001,10 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>floral</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -2199,11 +2063,6 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
           <t>floral</t>
         </is>
       </c>
@@ -2256,15 +2115,10 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -2318,15 +2172,10 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Walderdbeere</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
@@ -2380,15 +2229,10 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>floral</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
@@ -2442,15 +2286,10 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -2504,15 +2343,10 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
@@ -2566,15 +2400,10 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>floral</t>
+          <t>fruity</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
-        <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -2643,11 +2472,6 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
           <t>green</t>
         </is>
       </c>
@@ -2708,11 +2532,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2770,11 +2589,6 @@
           <t>green</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2829,11 +2643,6 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
           <t>green</t>
         </is>
       </c>
@@ -2891,11 +2700,6 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
           <t>green</t>
         </is>
       </c>
@@ -2953,11 +2757,6 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
           <t>green</t>
         </is>
       </c>
@@ -3010,15 +2809,10 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -3072,15 +2866,10 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>fruity</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
-        <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -3134,15 +2923,10 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>fruity</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
-        <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -3204,11 +2988,6 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3263,11 +3042,6 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
           <t>warm</t>
         </is>
       </c>
@@ -3325,11 +3099,6 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -3382,15 +3151,10 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>Walderdbeere</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -3444,15 +3208,10 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>fruity</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -3506,15 +3265,10 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -3568,15 +3322,10 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>Walderdbeere</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -3630,15 +3379,10 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
@@ -3692,15 +3436,10 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
@@ -3759,11 +3498,6 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
           <t>green</t>
         </is>
       </c>
@@ -3816,15 +3550,10 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -3878,15 +3607,10 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -3940,15 +3664,10 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -4010,11 +3729,6 @@
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4064,15 +3778,10 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>Walderdbeere</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -4126,15 +3835,10 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>floral</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -4206,11 +3910,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4260,15 +3959,10 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>floral</t>
+          <t>fruity</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
-        <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -4327,11 +4021,6 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
           <t>warm</t>
         </is>
       </c>
@@ -4384,15 +4073,10 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -4446,15 +4130,10 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -4516,11 +4195,6 @@
           <t>green</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4580,15 +4254,10 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -4650,11 +4319,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4712,11 +4376,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4766,15 +4425,10 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
@@ -4828,15 +4482,10 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>floral</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -4890,15 +4539,10 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>floral</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
@@ -4952,15 +4596,10 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>floral</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
@@ -5019,11 +4658,6 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -5081,11 +4715,6 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -5143,11 +4772,6 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
           <t>dairy</t>
         </is>
       </c>
@@ -5200,15 +4824,10 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>floral</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
@@ -5262,15 +4881,10 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>Walderdbeere</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
@@ -5324,15 +4938,10 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>floral</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -5391,11 +5000,6 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -5453,11 +5057,6 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
           <t>warm</t>
         </is>
       </c>
@@ -5510,15 +5109,10 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
@@ -5577,11 +5171,6 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -5634,15 +5223,10 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>green</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -5706,15 +5290,10 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -5768,15 +5347,10 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>floral</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -5830,15 +5404,10 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -5892,15 +5461,10 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
@@ -5954,15 +5518,10 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -6031,11 +5590,6 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -6096,11 +5650,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6158,11 +5707,6 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6212,15 +5756,10 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>floral</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
@@ -6274,15 +5813,10 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -6354,11 +5888,6 @@
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6408,15 +5937,10 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -6478,11 +6002,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6532,15 +6051,10 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>floral</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
@@ -6599,11 +6113,6 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
           <t>unpleasant</t>
         </is>
       </c>
@@ -6656,15 +6165,10 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
@@ -6718,15 +6222,10 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -6788,11 +6287,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6860,11 +6354,6 @@
           <t>green</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6919,11 +6408,6 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -6981,11 +6465,6 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -7046,11 +6525,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7105,11 +6579,6 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
           <t>green</t>
         </is>
       </c>
@@ -7162,15 +6631,10 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>Walderdbeere</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7224,15 +6688,10 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>floral</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -7286,15 +6745,10 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>fruity</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
-        <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7348,15 +6802,10 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7410,15 +6859,10 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7472,15 +6916,10 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>fruity</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
@@ -7534,15 +6973,10 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -7604,11 +7038,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7666,11 +7095,6 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7728,11 +7152,6 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7782,15 +7201,10 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>fruity</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
-        <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -7849,11 +7263,6 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
           <t>Walderdbeere</t>
         </is>
       </c>
@@ -7906,15 +7315,10 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>floral</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -7968,15 +7372,10 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
@@ -8040,15 +7439,10 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>fruity</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -8107,11 +7501,6 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
           <t>warm</t>
         </is>
       </c>
@@ -8164,15 +7553,10 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>floral</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -8226,15 +7610,10 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>fruity</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
-        <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -8288,15 +7667,10 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
@@ -8355,11 +7729,6 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
           <t>fruity</t>
         </is>
       </c>
@@ -8412,15 +7781,10 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>fruity</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
-        <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -8474,15 +7838,10 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
@@ -8551,11 +7910,6 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
           <t>floral</t>
         </is>
       </c>
@@ -8616,11 +7970,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8674,11 +8023,6 @@
         </is>
       </c>
       <c r="M131" t="inlineStr">
-        <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
@@ -8690,227 +8034,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster_Walderdbeere</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster_dairy</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster_floral</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster_fruity</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster_green</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster_unpleasant</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster_warm</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>M1_kw</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>185.621P
-187.894P
-188.976</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>185.291
-185.294
-185.471
-186.985P
-187.167P
-187.826P
-187.886P
-187.907
-187.921P
-187.923P
-188.402P
-188.656P</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>185.046
-185.321
-185.644P
-185.675P
-186.190P
-186.192
-186.981P
-187.015P
-187.776
-187.786P
-187.796P
-187.885P
-187.914P
-189.014</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>185.028
-185.513P
-185.727P
-187.004P
-187.695P
-187.772
-187.893P
-188.481KHP
-188.639P</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>185.086
-185.178HP
-185.382P
-185.507P
-186.569P
-187.246P
-187.482P
-187.483P
-187.519P
-187.657P
-187.746P
-187.787P
-187.834P
-187.920P
-188.375P
-188.412P
-188.560P
-188.820
-188.894</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>185.133
-185.267
-186.821
-187.414P
-187.773P
-187.829P</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>185.043P
-185.044
-185.090P
-185.091
-185.237H
-185.239
-185.309P
-185.314
-185.339P
-185.514
-185.578P
-185.615
-185.664
-185.741P
-185.748P
-185.796P
-185.902P
-185.922P
-185.984P
-186.179P
-186.277P
-186.293P
-186.395P
-186.396P
-186.490P
-186.950P
-187.061P
-187.064P
-187.119P
-187.365
-187.507P
-187.521P
-187.522P
-187.567P
-187.571P
-187.608P
-187.662P
-187.694P
-187.752P
-187.753P
-187.783P
-187.791P
-187.799P
-187.800P
-187.843P
-187.870P
-187.871P
-187.892P
-187.895P
-187.896P
-187.897P
-187.916P
-188.118P
-188.462KHP
-188.491P
-188.628P
-188.668P
-188.740P
-188.819
-188.822
-188.866
-188.977
-188.992
-189.012
-189.051
-189.068
-189.075</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9041,8 +8164,7 @@
 187.246P
 187.519P
 187.521P
-188.412P
-188.560P</t>
+188.412P</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -9067,6 +8189,7 @@
 187.885P
 187.895P
 188.375P
+188.560P
 188.639P
 188.819
 188.866
@@ -9131,7 +8254,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9352,1025 +8475,2083 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Strategy A</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Strategy B</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>NMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S1_target_recipes</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>S2_ingredients</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.556</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S1_target_recipes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>S3_hybrid</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.909</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S1_target_recipes</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.969</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S1_target_recipes</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S1_target_recipes</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.727</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S1_target_recipes</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.518</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S1_target_recipes</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.408</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S1_target_recipes</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.405</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S1_target_recipes</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.712</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S2_ingredients</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S3_hybrid</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S2_ingredients</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S2_ingredients</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S2_ingredients</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S2_ingredients</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S2_ingredients</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.324</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S2_ingredients</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.314</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S2_ingredients</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.616</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S3_hybrid</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.905</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S3_hybrid</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S3_hybrid</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.702</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S3_hybrid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S3_hybrid</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S3_hybrid</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.366</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S3_hybrid</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.569</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.703</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.511</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.401</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.393</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.504</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.394</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.319</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.309</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.587</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.428</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.352</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S6_contrast</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.702</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.281</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.279</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>M1_label_prop</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.986</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>M2_rule_based</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.323</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>M3_consensus</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:AE12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Strategy A</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Strategy B</t>
+          <t>ARI S1_target_recipes vs S2_ingredients</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NMI S1_target_recipes vs S2_ingredients</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>ARI S1_target_recipes vs S3_hybrid</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S1_target_recipes vs S3_hybrid</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S1_target_recipes vs S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S1_target_recipes vs S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S1_target_recipes vs S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S1_target_recipes vs S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S1_target_recipes vs S6_contrast</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S1_target_recipes vs S6_contrast</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S2_ingredients vs S3_hybrid</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S2_ingredients vs S3_hybrid</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S2_ingredients vs S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S2_ingredients vs S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S2_ingredients vs S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S2_ingredients vs S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S2_ingredients vs S6_contrast</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S2_ingredients vs S6_contrast</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S3_hybrid vs S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S3_hybrid vs S4_target_recipes_median</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S3_hybrid vs S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S3_hybrid vs S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S3_hybrid vs S6_contrast</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S3_hybrid vs S6_contrast</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S4_target_recipes_median vs S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S4_target_recipes_median vs S5_ingredients_median</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S4_target_recipes_median vs S6_contrast</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S4_target_recipes_median vs S6_contrast</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ARI S5_ingredients_median vs S6_contrast</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>NMI S5_ingredients_median vs S6_contrast</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S1_target_recipes</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>S2_ingredients</t>
-        </is>
+          <t>NearestCentroid</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.504</v>
       </c>
       <c r="C2" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0.504</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.556</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S1_target_recipes</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>S3_hybrid</t>
-        </is>
+          <t>k-Means</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8179999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.918</v>
+        <v>0.847</v>
       </c>
       <c r="D3" t="n">
-        <v>0.909</v>
+        <v>0.898</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.801</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S1_target_recipes</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>S4_target_recipes_median</t>
-        </is>
+          <t>k-Medoids</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.454</v>
       </c>
       <c r="C4" t="n">
-        <v>0.959</v>
+        <v>0.583</v>
       </c>
       <c r="D4" t="n">
-        <v>0.969</v>
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S1_target_recipes</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>S5_ingredients_median</t>
-        </is>
+          <t>GMM</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.302</v>
       </c>
       <c r="C5" t="n">
-        <v>0.462</v>
+        <v>0.375</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.906</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S1_target_recipes</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>S6_contrast</t>
-        </is>
+          <t>Fuzzy c-Means</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.754</v>
       </c>
       <c r="C6" t="n">
-        <v>0.63</v>
+        <v>0.777</v>
       </c>
       <c r="D6" t="n">
-        <v>0.727</v>
+        <v>0.413</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.834</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S1_target_recipes</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>M1_label_prop</t>
-        </is>
+          <t>SOM</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.702</v>
       </c>
       <c r="C7" t="n">
-        <v>0.304</v>
+        <v>0.85</v>
       </c>
       <c r="D7" t="n">
-        <v>0.518</v>
+        <v>0.897</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.856</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S1_target_recipes</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>M2_rule_based</t>
-        </is>
+          <t>DEC (simpl.)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.23</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.408</v>
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.008</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S1_target_recipes</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>M1_kw</t>
-        </is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.627</v>
       </c>
       <c r="C9" t="n">
-        <v>0.149</v>
+        <v>0.743</v>
       </c>
       <c r="D9" t="n">
-        <v>0.389</v>
+        <v>0.838</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.981</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S1_target_recipes</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>M2_kw</t>
-        </is>
+          <t>DBSCAN</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.614</v>
       </c>
       <c r="C10" t="n">
-        <v>0.22</v>
+        <v>0.589</v>
       </c>
       <c r="D10" t="n">
-        <v>0.392</v>
+        <v>0.597</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.862</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S1_target_recipes</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>M3_consensus</t>
-        </is>
+          <t>HDBSCAN</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.296</v>
       </c>
       <c r="C11" t="n">
-        <v>0.647</v>
+        <v>0.501</v>
       </c>
       <c r="D11" t="n">
-        <v>0.712</v>
+        <v>0.316</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.595</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S2_ingredients</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>S3_hybrid</t>
-        </is>
+          <t>Spectral</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.98</v>
       </c>
       <c r="C12" t="n">
-        <v>0.508</v>
+        <v>0.981</v>
       </c>
       <c r="D12" t="n">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S2_ingredients</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S2_ingredients</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>S2_ingredients</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>S6_contrast</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>S2_ingredients</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>M1_label_prop</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>S2_ingredients</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>M2_rule_based</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.324</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>S2_ingredients</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>M1_kw</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.287</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>S2_ingredients</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>M2_kw</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.183</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.307</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>S2_ingredients</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>M3_consensus</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.616</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>S3_hybrid</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.922</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.905</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>S3_hybrid</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>S3_hybrid</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>S6_contrast</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.702</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>S3_hybrid</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>M1_label_prop</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.279</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>S3_hybrid</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>M2_rule_based</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.369</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>S3_hybrid</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>M1_kw</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.356</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>S3_hybrid</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>M2_kw</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.354</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>S3_hybrid</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>M3_consensus</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.637</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.569</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>S6_contrast</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.703</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>M1_label_prop</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.511</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>M2_rule_based</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.401</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>M1_kw</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.379</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>M2_kw</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.386</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>M3_consensus</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>S6_contrast</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.504</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>M1_label_prop</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.394</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>M2_rule_based</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.319</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>M1_kw</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.332</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>M2_kw</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.302</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>M3_consensus</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.587</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>S6_contrast</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>M1_label_prop</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.428</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>S6_contrast</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>M2_rule_based</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.354</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>S6_contrast</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>M1_kw</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.342</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>S6_contrast</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>M2_kw</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>S6_contrast</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>M3_consensus</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.702</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>M1_label_prop</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>M2_rule_based</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.281</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>M1_label_prop</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>M1_kw</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.658</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>M1_label_prop</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>M2_kw</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.279</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>M1_label_prop</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>M3_consensus</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.543</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>M2_rule_based</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>M1_kw</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.221</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>M2_rule_based</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>M2_kw</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>M2_rule_based</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>M3_consensus</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.323</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>M1_kw</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>M2_kw</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.237</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>M1_kw</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>M3_consensus</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.367</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>M2_kw</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>M3_consensus</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.303</v>
+        <v>0.98</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10384,1952 +10565,608 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE12"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Algorithm</t>
+          <t>Recipe</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ARI S1_target_recipes vs S2_ingredients</t>
+          <t>matched</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>NMI S1_target_recipes vs S2_ingredients</t>
+          <t>old_M1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ARI S1_target_recipes vs S3_hybrid</t>
+          <t>new_M1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>NMI S1_target_recipes vs S3_hybrid</t>
+          <t>M1_change</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ARI S1_target_recipes vs S4_target_recipes_median</t>
+          <t>old_M2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>NMI S1_target_recipes vs S4_target_recipes_median</t>
+          <t>new_M2</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>ARI S1_target_recipes vs S5_ingredients_median</t>
+          <t>M2_change</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NMI S1_target_recipes vs S5_ingredients_median</t>
+          <t>M2_kw</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>ARI S1_target_recipes vs S6_contrast</t>
+          <t>M2kw_vs_M2</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>NMI S1_target_recipes vs S6_contrast</t>
+          <t>kw_vote</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>ARI S2_ingredients vs S3_hybrid</t>
+          <t>panel_%</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>NMI S2_ingredients vs S3_hybrid</t>
+          <t>Cluster_vorgegeben</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ARI S2_ingredients vs S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>NMI S2_ingredients vs S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ARI S2_ingredients vs S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>NMI S2_ingredients vs S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>ARI S2_ingredients vs S6_contrast</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>NMI S2_ingredients vs S6_contrast</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>ARI S3_hybrid vs S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>NMI S3_hybrid vs S4_target_recipes_median</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>ARI S3_hybrid vs S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>NMI S3_hybrid vs S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>ARI S3_hybrid vs S6_contrast</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>NMI S3_hybrid vs S6_contrast</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>ARI S4_target_recipes_median vs S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>NMI S4_target_recipes_median vs S5_ingredients_median</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>ARI S4_target_recipes_median vs S6_contrast</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>NMI S4_target_recipes_median vs S6_contrast</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>ARI S5_ingredients_median vs S6_contrast</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>NMI S5_ingredients_median vs S6_contrast</t>
+          <t>Jan_Free_Sorting</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NearestCentroid</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.727</v>
-      </c>
+          <t>185.237</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>185.237H</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.922</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.504</v>
+        <v>100</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Karamell</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Karamell</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>k-Means</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.898</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.906</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.931</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.931</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.799</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.82</v>
-      </c>
+          <t>185.507</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>185.507P</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.831</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.849</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.916</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.777</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.747</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.801</v>
+        <v>25</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>buttrig</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Heidelbeere/ Jasmin</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>k-Medoids</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.454</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.646</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.6830000000000001</v>
-      </c>
+          <t>185.044</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>185.044</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.646</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.787</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.771</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.71</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>grün</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GMM</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.906</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.902</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.497</v>
-      </c>
+          <t>187.920</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>187.920P</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.906</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.902</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.45</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>grün - reif/ muffig</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fuzzy c-Means</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.777</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.661</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.636</v>
-      </c>
+          <t>187.894</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>187.894P</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.777</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.646</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.661</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.874</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.834</v>
+        <v>100</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOM</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.897</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.866</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.899</v>
-      </c>
+          <t>188.976</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>188.976</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.717</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.837</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.897</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.872</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.834</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.866</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.899</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.856</v>
+        <v>25</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>nicht verkostet</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>nicht verkostet</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DEC (simpl.)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
+          <t>186.179</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>186.179P</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.849</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.849</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.008</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>blumig</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ward</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.768</v>
-      </c>
+          <t>186.396</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>186.396P</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.8129999999999999</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.872</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.8090000000000001</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.856</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.893</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.981</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>blumig</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DBSCAN</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.577</v>
-      </c>
+          <t>187.796P</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>187.796P</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.899</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.898</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.851</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.898</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.862</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.862</v>
+        <v>50</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>grün</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Heidelbeere/ Jasmin</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDBSCAN</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.454</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.62</v>
-      </c>
+          <t>189.014</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>189.014</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.947</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.908</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.601</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.908</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.853</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.782</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.372</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.595</v>
+        <v>75</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>nicht verkostet</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>nicht verkostet</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spectral</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Recipe</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>old_M1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>new_M1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>M1_change</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>M1_kw</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>M1kw_vs_M1</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>old_M2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>new_M2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>M2_change</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>M2_kw</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>M2kw_vs_M2</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>kw_vote</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>panel_%</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster_vorgegeben</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Jan_Free_Sorting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>185.237</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>185.237H</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>100</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Karamell</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Karamell</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>185.507</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>185.507P</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>25</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>buttrig</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Heidelbeere/ Jasmin</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>185.044</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>185.044</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>50</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>grün</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>187.920</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>187.920P</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>75</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>grün - reif/ muffig</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>187.894</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>187.894P</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>100</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>188.976</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>188.976</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>25</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>nicht verkostet</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>nicht verkostet</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>186.179</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>186.179P</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>50</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>blumig</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>186.396</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>186.396P</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Walderdbeere</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>25</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>blumig</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>187.796P</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>187.796P</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>grün</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Heidelbeere/ Jasmin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>189.014</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>189.014</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>75</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>nicht verkostet</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>nicht verkostet</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>186.981P</t>
         </is>
       </c>
@@ -12351,33 +11188,27 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>50</v>
+      </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>50</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12406,34 +11237,28 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
         <v>50</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>buttrig - grün</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12462,34 +11287,28 @@
           <t>green</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
         <v>100</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>grün</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>grün</t>
         </is>
@@ -12519,37 +11338,27 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>green</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
           <t>green</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>25</v>
+      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>25</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12575,45 +11384,31 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>floral</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
           <t>floral</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>75</v>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>75</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
           <t>blumig</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12642,34 +11437,28 @@
           <t>green</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
         <v>50</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Karamell</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12698,38 +11487,28 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>75</v>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>75</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
           <t>buttrig</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>muffig/ buttrig</t>
         </is>
@@ -12764,14 +11543,10 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>warm</t>
@@ -12783,21 +11558,15 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>50</v>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>50</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
           <t>nicht verkostet</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>nicht verkostet</t>
         </is>
@@ -12830,30 +11599,24 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>50</v>
+      </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>50</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12882,34 +11645,28 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
         <v>50</v>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>grün</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12938,10 +11695,14 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>RISK (panel liked old)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -12949,31 +11710,17 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>RISK (panel liked old)</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>100</v>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>100</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
           <t>muffig</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Heidelbeere/ Jasmin</t>
         </is>
@@ -13003,49 +11750,39 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>RISK (panel liked old)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>floral</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>RISK (panel liked old)</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
+      <c r="L23" t="n">
         <v>75</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13074,34 +11811,28 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
         <v>75</v>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>reif/muffig</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13127,49 +11858,31 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>50</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>50</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
           <t>reif/muffig</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13198,38 +11911,28 @@
           <t>fruity</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>75</v>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
-        <v>75</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
           <t>blumig</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Birne/ Marille (Outlayer)</t>
         </is>
@@ -13259,33 +11962,27 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>100</v>
+      </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
-        <v>100</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13314,34 +12011,28 @@
           <t>fruity</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
         <v>50</v>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>reif/ muffig</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13367,37 +12058,31 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>fruity</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>unpleasant</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
         <v>25</v>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>reif/muffig</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/cluster_assignments_expert_seeded_all_strategies.xlsx
+++ b/outputs/cluster_assignments_expert_seeded_all_strategies.xlsx
@@ -4249,12 +4249,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>green</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>green</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>fruity</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>fruity</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -8153,6 +8153,7 @@
 187.061P
 187.752P
 187.753P
+187.772
 187.871P
 188.822</t>
         </is>
@@ -8164,6 +8165,7 @@
 187.246P
 187.519P
 187.521P
+187.657P
 188.412P</t>
         </is>
       </c>
@@ -8175,12 +8177,12 @@
 185.090P
 185.091
 185.133
+185.267
 185.514
 185.615
 185.741P
 186.293P
 186.821
-187.657P
 187.773P
 187.787P
 187.799P
@@ -8199,7 +8201,6 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>185.237H
-185.267
 185.309P
 185.314
 185.321
@@ -8229,7 +8230,6 @@
 187.608P
 187.694P
 187.695P
-187.772
 187.800P
 187.870P
 187.893P
@@ -8626,10 +8626,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.23</v>
+        <v>0.251</v>
       </c>
       <c r="D8" t="n">
-        <v>0.408</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="9">
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.231</v>
+        <v>0.252</v>
       </c>
       <c r="D9" t="n">
-        <v>0.405</v>
+        <v>0.419</v>
       </c>
     </row>
     <row r="10">
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.194</v>
+        <v>0.208</v>
       </c>
       <c r="D16" t="n">
-        <v>0.324</v>
+        <v>0.341</v>
       </c>
     </row>
     <row r="17">
@@ -8788,10 +8788,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.192</v>
+        <v>0.206</v>
       </c>
       <c r="D17" t="n">
-        <v>0.314</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="18">
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.212</v>
+        <v>0.232</v>
       </c>
       <c r="D23" t="n">
-        <v>0.369</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="24">
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.213</v>
+        <v>0.232</v>
       </c>
       <c r="D24" t="n">
-        <v>0.366</v>
+        <v>0.379</v>
       </c>
     </row>
     <row r="25">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.223</v>
+        <v>0.244</v>
       </c>
       <c r="D29" t="n">
-        <v>0.401</v>
+        <v>0.415</v>
       </c>
     </row>
     <row r="30">
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.221</v>
+        <v>0.242</v>
       </c>
       <c r="D30" t="n">
-        <v>0.393</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="31">
@@ -9097,7 +9097,7 @@
         <v>0.193</v>
       </c>
       <c r="D34" t="n">
-        <v>0.319</v>
+        <v>0.316</v>
       </c>
     </row>
     <row r="35">
@@ -9115,7 +9115,7 @@
         <v>0.19</v>
       </c>
       <c r="D35" t="n">
-        <v>0.309</v>
+        <v>0.305</v>
       </c>
     </row>
     <row r="36">
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.202</v>
+        <v>0.22</v>
       </c>
       <c r="D38" t="n">
-        <v>0.354</v>
+        <v>0.367</v>
       </c>
     </row>
     <row r="39">
@@ -9184,10 +9184,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.203</v>
+        <v>0.221</v>
       </c>
       <c r="D39" t="n">
-        <v>0.352</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="40">
@@ -9220,10 +9220,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.103</v>
+        <v>0.123</v>
       </c>
       <c r="D41" t="n">
-        <v>0.281</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="42">
@@ -9238,10 +9238,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.104</v>
+        <v>0.124</v>
       </c>
       <c r="D42" t="n">
-        <v>0.279</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="43">
@@ -9292,10 +9292,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.171</v>
+        <v>0.195</v>
       </c>
       <c r="D45" t="n">
-        <v>0.323</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="46">
@@ -9310,10 +9310,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.17</v>
+        <v>0.193</v>
       </c>
       <c r="D46" t="n">
-        <v>0.315</v>
+        <v>0.336</v>
       </c>
     </row>
   </sheetData>
@@ -11697,17 +11697,13 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>RISK (panel liked old)</t>
-        </is>
-      </c>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>unpleasant</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -23308,6 +23304,7 @@
 187.061P
 187.752P
 187.753P
+187.772
 187.871P
 188.822</t>
         </is>
@@ -23318,6 +23315,7 @@
 186.569P
 187.519P
 187.521P
+187.657P
 188.412P</t>
         </is>
       </c>
@@ -23329,12 +23327,12 @@
 185.090P
 185.091
 185.133
+185.267
 185.514
 185.615
 185.741P
 186.293P
 186.821
-187.657P
 187.773P
 187.787P
 187.799P
@@ -23353,7 +23351,6 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>185.237H
-185.267
 185.309P
 185.314
 185.321
@@ -23383,7 +23380,6 @@
 187.608P
 187.694P
 187.695P
-187.772
 187.800P
 187.870P
 187.893P

--- a/outputs/cluster_assignments_expert_seeded_all_strategies.xlsx
+++ b/outputs/cluster_assignments_expert_seeded_all_strategies.xlsx
@@ -21,6 +21,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement_Strategies" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement_byAlgo" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verkostung_Compare" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_Scorecard" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs_Retaste" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10661,7 +10663,6 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>warm</t>
@@ -10672,14 +10673,11 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>100</v>
       </c>
@@ -10715,7 +10713,6 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>warm</t>
@@ -10726,14 +10723,11 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>25</v>
       </c>
@@ -10769,7 +10763,6 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>unpleasant</t>
@@ -10780,14 +10773,11 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>50</v>
       </c>
@@ -10796,7 +10786,6 @@
           <t>grün</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10819,7 +10808,6 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>warm</t>
@@ -10830,14 +10818,11 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>75</v>
       </c>
@@ -10846,7 +10831,6 @@
           <t>grün - reif/ muffig</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10869,7 +10853,6 @@
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Walderdbeere</t>
@@ -10880,14 +10863,11 @@
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>100</v>
       </c>
@@ -10923,7 +10903,6 @@
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Walderdbeere</t>
@@ -10934,14 +10913,11 @@
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>25</v>
       </c>
@@ -10977,7 +10953,6 @@
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>warm</t>
@@ -10988,14 +10963,11 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>50</v>
       </c>
@@ -11004,7 +10976,6 @@
           <t>blumig</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11027,7 +10998,6 @@
           <t>Walderdbeere</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>warm</t>
@@ -11038,14 +11008,11 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>25</v>
       </c>
@@ -11054,7 +11021,6 @@
           <t>blumig</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11077,7 +11043,6 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>floral</t>
@@ -11088,14 +11053,11 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>50</v>
       </c>
@@ -11131,7 +11093,6 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>floral</t>
@@ -11142,14 +11103,11 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>75</v>
       </c>
@@ -11185,7 +11143,6 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>warm</t>
@@ -11196,19 +11153,14 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>50</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11231,7 +11183,6 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>floral</t>
@@ -11242,14 +11193,11 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>50</v>
       </c>
@@ -11258,7 +11206,6 @@
           <t>buttrig - grün</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11281,7 +11228,6 @@
           <t>green</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>green</t>
@@ -11292,14 +11238,11 @@
           <t>green</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>100</v>
       </c>
@@ -11335,7 +11278,6 @@
           <t>green</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>green</t>
@@ -11346,19 +11288,14 @@
           <t>green</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>25</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11381,7 +11318,6 @@
           <t>green</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>floral</t>
@@ -11392,14 +11328,11 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>floral</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>75</v>
       </c>
@@ -11408,7 +11341,6 @@
           <t>blumig</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11431,7 +11363,6 @@
           <t>green</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>green</t>
@@ -11442,14 +11373,11 @@
           <t>green</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>50</v>
       </c>
@@ -11458,7 +11386,6 @@
           <t>Karamell</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11481,7 +11408,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>dairy</t>
@@ -11492,14 +11418,11 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>75</v>
       </c>
@@ -11535,7 +11458,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>warm</t>
@@ -11546,13 +11468,11 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>warm</t>
@@ -11593,7 +11513,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>dairy</t>
@@ -11604,19 +11523,14 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>50</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11639,7 +11553,6 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>dairy</t>
@@ -11650,14 +11563,11 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>dairy</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
         <v>50</v>
       </c>
@@ -11666,7 +11576,6 @@
           <t>grün</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11689,7 +11598,6 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>unpleasant</t>
@@ -11700,14 +11608,11 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
         <v>100</v>
       </c>
@@ -11743,7 +11648,6 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>warm</t>
@@ -11777,8 +11681,6 @@
       <c r="L23" t="n">
         <v>75</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11801,7 +11703,6 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>unpleasant</t>
@@ -11812,14 +11713,11 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>75</v>
       </c>
@@ -11828,7 +11726,6 @@
           <t>reif/muffig</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11851,7 +11748,6 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>unpleasant</t>
@@ -11862,14 +11758,11 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>50</v>
       </c>
@@ -11878,7 +11771,6 @@
           <t>reif/muffig</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11901,7 +11793,6 @@
           <t>fruity</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>fruity</t>
@@ -11912,14 +11803,11 @@
           <t>fruity</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>75</v>
       </c>
@@ -11955,7 +11843,6 @@
           <t>fruity</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>warm</t>
@@ -11966,19 +11853,14 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
         <v>100</v>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12001,7 +11883,6 @@
           <t>fruity</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>fruity</t>
@@ -12012,14 +11893,11 @@
           <t>fruity</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>fruity</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>50</v>
       </c>
@@ -12028,7 +11906,6 @@
           <t>reif/ muffig</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12051,7 +11928,6 @@
           <t>fruity</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>unpleasant</t>
@@ -12062,14 +11938,11 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
         <v>25</v>
       </c>
@@ -12078,7 +11951,958 @@
           <t>reif/muffig</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recipe</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>src</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>185.237</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>endorsed</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>warm ✓</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>warm ✓</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>warm ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>187.920</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>endorsed</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>warm ✓</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>warm ✓</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>warm ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>187.894</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>endorsed</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Walderdbeere ✓</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Walderdbeere ✓</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Walderdbeere ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>189.014</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>endorsed</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>floral ✓</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>floral ✓</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>floral ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>188.412P</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>endorsed</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>green ✓</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>green ✓</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>green ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>185.294</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>endorsed</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dairy ✓</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>dairy ✓</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>dairy ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>187.167P</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>corrected</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dairy ✗</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>dairy ✗</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>dairy ✗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>185.267</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>endorsed</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>unpleasant ✓</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>unpleasant ✓</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>unpleasant ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>187.829P</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>endorsed</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>unpleasant ✓</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>unpleasant ✓</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>unpleasant ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>185.028</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>endorsed</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>fruity ✓</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>fruity ✓</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>fruity ✓</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recipe</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>panel_%</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>M2_kw</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>185.507</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>panel split</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>185.044</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>50</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>M1≠M2 (cluster shown unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>188.976</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>panel split</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>186.179</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>M1≠M2 (cluster shown unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>186.396</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>M1≠M2 (cluster shown unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>187.796P</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>panel split</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>186.981P</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>M1≠M2 (cluster shown unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>185.046</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>panel split</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>187.521P</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>25</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>panel split</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>185.902</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>75</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>M1≠M2 (cluster shown unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>185.178</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>50</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>panel split</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>188.977</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>50</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>M1≠M2 (cluster shown unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>187.826P</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>50</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>panel split</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>187.246P</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>75</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>M1≠M2 (cluster shown unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>188.560P</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>50</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>panel split</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>187.004P</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>M1≠M2 (cluster shown unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>185.513P</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>50</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>panel split</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>188.639P</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>25</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>M1≠M2 (cluster shown unknown)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
